--- a/Team-Data/2007-08/12-6-2007-08.xlsx
+++ b/Team-Data/2007-08/12-6-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,88 +728,88 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.444</v>
+        <v>0.412</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="J2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.441</v>
+        <v>0.444</v>
       </c>
       <c r="L2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.301</v>
+        <v>0.311</v>
       </c>
       <c r="O2" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="P2" t="n">
-        <v>27.1</v>
+        <v>26.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R2" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S2" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U2" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V2" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X2" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>93.3</v>
+        <v>93.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>16</v>
@@ -751,43 +818,43 @@
         <v>19</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>26</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>27</v>
       </c>
       <c r="AK2" t="n">
         <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
       </c>
       <c r="AR2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>24</v>
@@ -799,13 +866,13 @@
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>13.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -939,7 +1006,7 @@
         <v>17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>4</v>
@@ -969,10 +1036,10 @@
         <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>18</v>
@@ -981,7 +1048,7 @@
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1170,22 @@
         <v>-5.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
         <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>14</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
         <v>23</v>
@@ -1151,22 +1218,22 @@
         <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
@@ -1175,7 +1242,7 @@
         <v>19</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
         <v>26</v>
@@ -1318,13 +1385,13 @@
         <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
         <v>24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1360,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="AJ6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK6" t="n">
         <v>26</v>
@@ -1497,7 +1564,7 @@
         <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1509,7 +1576,7 @@
         <v>25</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -1518,10 +1585,10 @@
         <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
         <v>18</v>
@@ -1542,7 +1609,7 @@
         <v>17</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.632</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
@@ -1589,94 +1656,94 @@
         <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>79.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="O7" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="R7" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W7" t="n">
         <v>5.7</v>
       </c>
-      <c r="M7" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O7" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="P7" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.846</v>
-      </c>
-      <c r="R7" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="X7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.5</v>
+        <v>102.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
       </c>
       <c r="AF7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN7" t="n">
         <v>23</v>
@@ -1691,13 +1758,13 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
         <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>17</v>
@@ -1706,25 +1773,25 @@
         <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -1753,94 +1820,94 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.579</v>
       </c>
       <c r="H8" t="n">
         <v>48</v>
       </c>
       <c r="I8" t="n">
-        <v>38.8</v>
+        <v>38.4</v>
       </c>
       <c r="J8" t="n">
-        <v>84.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L8" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M8" t="n">
-        <v>19.2</v>
+        <v>19.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.349</v>
+        <v>0.345</v>
       </c>
       <c r="O8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="P8" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.737</v>
+        <v>0.739</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
         <v>33.5</v>
       </c>
       <c r="T8" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U8" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="W8" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AC8" t="n">
         <v>4.6</v>
       </c>
-      <c r="Z8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>19</v>
@@ -1858,10 +1925,10 @@
         <v>12</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>3</v>
@@ -1870,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
@@ -1882,19 +1949,19 @@
         <v>5</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ8" t="n">
         <v>21</v>
@@ -1903,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -2052,16 +2119,16 @@
         <v>21</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
         <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2237,7 +2304,7 @@
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
         <v>17</v>
@@ -2264,7 +2331,7 @@
         <v>24</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>11</v>
@@ -2398,13 +2465,13 @@
         <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>28</v>
@@ -2437,7 +2504,7 @@
         <v>12</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>14</v>
@@ -2589,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
@@ -2628,7 +2695,7 @@
         <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>8</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>-5.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
         <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2783,13 +2850,13 @@
         <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS13" t="n">
         <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
         <v>20</v>
@@ -2816,7 +2883,7 @@
         <v>22</v>
       </c>
       <c r="BC13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH14" t="n">
         <v>19</v>
@@ -2965,7 +3032,7 @@
         <v>8</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
@@ -2977,7 +3044,7 @@
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
@@ -2986,7 +3053,7 @@
         <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ14" t="n">
         <v>20</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>-1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF15" t="n">
         <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
         <v>15</v>
@@ -3141,7 +3208,7 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
         <v>14</v>
@@ -3159,13 +3226,13 @@
         <v>13</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -3209,91 +3276,91 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.222</v>
+        <v>0.235</v>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>34.4</v>
+        <v>33.9</v>
       </c>
       <c r="J16" t="n">
-        <v>76.3</v>
+        <v>75.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.452</v>
+        <v>0.448</v>
       </c>
       <c r="L16" t="n">
         <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.34</v>
+        <v>0.333</v>
       </c>
       <c r="O16" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P16" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.667</v>
+        <v>0.674</v>
       </c>
       <c r="R16" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="S16" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="T16" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="U16" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="V16" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="X16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>90.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="AC16" t="n">
         <v>-5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>28</v>
       </c>
       <c r="AF16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG16" t="n">
         <v>28</v>
@@ -3302,13 +3369,13 @@
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3320,7 +3387,7 @@
         <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
         <v>19</v>
@@ -3332,28 +3399,28 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
       </c>
       <c r="AU16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
         <v>18</v>
@@ -3362,7 +3429,7 @@
         <v>29</v>
       </c>
       <c r="BC16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
@@ -3487,10 +3554,10 @@
         <v>16</v>
       </c>
       <c r="AJ17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
         <v>27</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>0.118</v>
+        <v>0.125</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3591,67 +3658,67 @@
         <v>36.4</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>81.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>0.445</v>
       </c>
       <c r="L18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M18" t="n">
-        <v>16.5</v>
+        <v>16.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O18" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="P18" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.716</v>
+        <v>0.713</v>
       </c>
       <c r="R18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="S18" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>40.4</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="V18" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W18" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y18" t="n">
         <v>4.7</v>
       </c>
-      <c r="Y18" t="n">
-        <v>5.1</v>
-      </c>
       <c r="Z18" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>92.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,19 +3733,19 @@
         <v>19</v>
       </c>
       <c r="AI18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM18" t="n">
         <v>17</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>18</v>
       </c>
       <c r="AN18" t="n">
         <v>17</v>
@@ -3693,28 +3760,28 @@
         <v>24</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
         <v>20</v>
       </c>
       <c r="AY18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
@@ -3875,7 +3942,7 @@
         <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS19" t="n">
         <v>19</v>
@@ -3887,7 +3954,7 @@
         <v>10</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
@@ -3908,7 +3975,7 @@
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
         <v>7</v>
@@ -4048,7 +4115,7 @@
         <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
         <v>28</v>
@@ -4063,7 +4130,7 @@
         <v>12</v>
       </c>
       <c r="AT20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
         <v>23</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -4197,16 +4264,16 @@
         <v>-7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
         <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>1</v>
@@ -4224,7 +4291,7 @@
         <v>24</v>
       </c>
       <c r="AM21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN21" t="n">
         <v>24</v>
@@ -4239,10 +4306,10 @@
         <v>26</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT21" t="n">
         <v>16</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4500,7 @@
         <v>12</v>
       </c>
       <c r="AV22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW22" t="n">
         <v>25</v>
@@ -4445,7 +4512,7 @@
         <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4573,25 +4640,25 @@
         <v>27</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM23" t="n">
         <v>27</v>
       </c>
       <c r="AN23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO23" t="n">
         <v>18</v>
@@ -4606,10 +4673,10 @@
         <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
         <v>21</v>
@@ -4621,10 +4688,10 @@
         <v>19</v>
       </c>
       <c r="AX23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY23" t="n">
         <v>12</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>13</v>
       </c>
       <c r="AZ23" t="n">
         <v>13</v>
@@ -4633,7 +4700,7 @@
         <v>22</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4773,7 +4840,7 @@
         <v>3</v>
       </c>
       <c r="AN24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="n">
         <v>20</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -4847,115 +4914,115 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.368</v>
+        <v>0.333</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="J25" t="n">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.457</v>
+        <v>0.454</v>
       </c>
       <c r="L25" t="n">
         <v>5.8</v>
       </c>
       <c r="M25" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O25" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="P25" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.727</v>
+        <v>0.725</v>
       </c>
       <c r="R25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S25" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T25" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="U25" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="V25" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="AD25" t="n">
         <v>15</v>
       </c>
-      <c r="W25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="AE25" t="n">
         <v>21</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>20</v>
       </c>
       <c r="AF25" t="n">
         <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AH25" t="n">
         <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>28</v>
@@ -4967,7 +5034,7 @@
         <v>22</v>
       </c>
       <c r="AR25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
         <v>26</v>
@@ -4979,28 +5046,28 @@
         <v>16</v>
       </c>
       <c r="AV25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW25" t="n">
         <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
         <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC25" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -5107,28 +5174,28 @@
         <v>-3</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>1</v>
       </c>
       <c r="AI26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ26" t="n">
         <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>22</v>
@@ -5149,7 +5216,7 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS26" t="n">
         <v>24</v>
@@ -5161,7 +5228,7 @@
         <v>30</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>9.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -5304,7 +5371,7 @@
         <v>19</v>
       </c>
       <c r="AI27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>-8</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
       </c>
       <c r="AF28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG28" t="n">
         <v>29</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5674,7 +5741,7 @@
         <v>7</v>
       </c>
       <c r="AK29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL29" t="n">
         <v>4</v>
@@ -5695,13 +5762,13 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -5716,7 +5783,7 @@
         <v>28</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>11</v>
@@ -5728,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>5</v>
@@ -5877,7 +5944,7 @@
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5898,7 +5965,7 @@
         <v>23</v>
       </c>
       <c r="AY30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ30" t="n">
         <v>27</v>
@@ -5907,7 +5974,7 @@
         <v>4</v>
       </c>
       <c r="BB30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC30" t="n">
         <v>4</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6029,16 +6096,16 @@
         <v>14</v>
       </c>
       <c r="AH31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI31" t="n">
         <v>10</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
         <v>14</v>
@@ -6047,10 +6114,10 @@
         <v>16</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP31" t="n">
         <v>13</v>
@@ -6059,7 +6126,7 @@
         <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS31" t="n">
         <v>13</v>
@@ -6071,7 +6138,7 @@
         <v>19</v>
       </c>
       <c r="AV31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW31" t="n">
         <v>15</v>
@@ -6080,7 +6147,7 @@
         <v>3</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-6-2007-08</t>
+          <t>2007-12-06</t>
         </is>
       </c>
     </row>
